--- a/plot/sensitivity_D.xlsx
+++ b/plot/sensitivity_D.xlsx
@@ -436,32 +436,32 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Unit Cost (元/kWh)</t>
+          <t>LCOE (元/kWh)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Investment Cost (万元)</t>
+          <t>Equipment Investment (万元, one-time)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Grid Cost (万元)</t>
+          <t>Annual Grid Cost (万元/yr)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Connection Cost (万元)</t>
+          <t>Connection Cost (万元, one-time)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Market Revenue (万元)</t>
+          <t>Annual Market Revenue (万元/yr)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Objective (万元)</t>
+          <t>Annualized Objective (万元/yr)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -490,34 +490,34 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02224480551834971</v>
+        <v>0.1959842690694846</v>
       </c>
       <c r="C2" t="n">
-        <v>13329.97505794663</v>
+        <v>167379.430045784</v>
       </c>
       <c r="D2" t="n">
-        <v>11749.28398782329</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>1000</v>
       </c>
       <c r="F2" t="n">
-        <v>5637.853770780544</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>20441.40527498597</v>
+        <v>16679.90064510335</v>
       </c>
       <c r="H2" t="n">
-        <v>192.8860836475713</v>
+        <v>86.00713363009163</v>
       </c>
       <c r="I2" t="n">
-        <v>50.84921854256438</v>
+        <v>143.0186325379542</v>
       </c>
       <c r="J2" t="n">
-        <v>69.09881057955671</v>
+        <v>485.7970673756182</v>
       </c>
       <c r="K2" t="n">
-        <v>18.86526009605538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -525,34 +525,34 @@
         <v>20</v>
       </c>
       <c r="B3" t="n">
-        <v>0.02466905669799192</v>
+        <v>0.1980936699523897</v>
       </c>
       <c r="C3" t="n">
-        <v>14593.15282945528</v>
+        <v>168191.7169200724</v>
       </c>
       <c r="D3" t="n">
-        <v>11749.28398782329</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>2000</v>
       </c>
       <c r="F3" t="n">
-        <v>5855.264971156765</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>22487.17184611826</v>
+        <v>17755.99468772663</v>
       </c>
       <c r="H3" t="n">
-        <v>209.9055632512516</v>
+        <v>86.94754087686988</v>
       </c>
       <c r="I3" t="n">
-        <v>63.7975675786101</v>
+        <v>144.9834320545083</v>
       </c>
       <c r="J3" t="n">
-        <v>65.01846074111026</v>
+        <v>483.5210851839864</v>
       </c>
       <c r="K3" t="n">
-        <v>18.86526009605538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -560,34 +560,34 @@
         <v>30</v>
       </c>
       <c r="B4" t="n">
-        <v>0.02812902251607754</v>
+        <v>0.1962923031382185</v>
       </c>
       <c r="C4" t="n">
-        <v>11935.01689595763</v>
+        <v>165644.076801232</v>
       </c>
       <c r="D4" t="n">
-        <v>11749.28398782329</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>3000</v>
       </c>
       <c r="F4" t="n">
-        <v>5559.890891916728</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>21124.40999186098</v>
+        <v>18517.33487192985</v>
       </c>
       <c r="H4" t="n">
-        <v>166.2734331295353</v>
+        <v>76.98933608601322</v>
       </c>
       <c r="I4" t="n">
-        <v>50.84921854256438</v>
+        <v>147.5793668631472</v>
       </c>
       <c r="J4" t="n">
-        <v>76.27697150718423</v>
+        <v>501.1777672711995</v>
       </c>
       <c r="K4" t="n">
-        <v>18.86526009605538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -595,34 +595,34 @@
         <v>40</v>
       </c>
       <c r="B5" t="n">
-        <v>0.03159306284661773</v>
+        <v>0.2004215584482251</v>
       </c>
       <c r="C5" t="n">
-        <v>15349.38023940166</v>
+        <v>168191.716920072</v>
       </c>
       <c r="D5" t="n">
-        <v>11749.28398782329</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>4000</v>
       </c>
       <c r="F5" t="n">
-        <v>5506.016540585714</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>25592.64768663493</v>
+        <v>19755.9946877266</v>
       </c>
       <c r="H5" t="n">
-        <v>202.7189316872619</v>
+        <v>86.94754087686852</v>
       </c>
       <c r="I5" t="n">
-        <v>96.18259535610666</v>
+        <v>144.9834320545087</v>
       </c>
       <c r="J5" t="n">
-        <v>82.81198710109975</v>
+        <v>483.5210851839887</v>
       </c>
       <c r="K5" t="n">
-        <v>18.86526009605538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -630,34 +630,34 @@
         <v>50</v>
       </c>
       <c r="B6" t="n">
-        <v>0.03388785632716831</v>
+        <v>0.2011212020879525</v>
       </c>
       <c r="C6" t="n">
-        <v>13582.90191747003</v>
+        <v>167792.8141298215</v>
       </c>
       <c r="D6" t="n">
-        <v>11749.28398782329</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>5000</v>
       </c>
       <c r="F6" t="n">
-        <v>5646.730809946374</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>24685.45509534328</v>
+        <v>20718.6259613755</v>
       </c>
       <c r="H6" t="n">
-        <v>196.8711741162136</v>
+        <v>74.78175886784675</v>
       </c>
       <c r="I6" t="n">
-        <v>55.51753014637408</v>
+        <v>158.6441210180155</v>
       </c>
       <c r="J6" t="n">
-        <v>61.82140961400067</v>
+        <v>502.2034833580587</v>
       </c>
       <c r="K6" t="n">
-        <v>18.86526009605538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -665,34 +665,34 @@
         <v>60</v>
       </c>
       <c r="B7" t="n">
-        <v>0.03672332201773229</v>
+        <v>0.2022851463358705</v>
       </c>
       <c r="C7" t="n">
-        <v>11112.39518972532</v>
+        <v>167792.8141298217</v>
       </c>
       <c r="D7" t="n">
-        <v>11749.28398782329</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>6000</v>
       </c>
       <c r="F7" t="n">
-        <v>5573.477033171194</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>23288.20214437423</v>
+        <v>21718.62596137552</v>
       </c>
       <c r="H7" t="n">
-        <v>137.0604511902589</v>
+        <v>74.78175886784811</v>
       </c>
       <c r="I7" t="n">
-        <v>71.71317269095394</v>
+        <v>158.6441210180144</v>
       </c>
       <c r="J7" t="n">
-        <v>92.85897362147894</v>
+        <v>502.2034833580567</v>
       </c>
       <c r="K7" t="n">
-        <v>18.86526009605538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -700,34 +700,34 @@
         <v>70</v>
       </c>
       <c r="B8" t="n">
-        <v>0.03978203280586762</v>
+        <v>0.2039133911919788</v>
       </c>
       <c r="C8" t="n">
-        <v>12928.31887112418</v>
+        <v>168191.716920072</v>
       </c>
       <c r="D8" t="n">
-        <v>11749.28398782329</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>7000</v>
       </c>
       <c r="F8" t="n">
-        <v>5594.960269720868</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>26082.64258922328</v>
+        <v>22755.9946877266</v>
       </c>
       <c r="H8" t="n">
-        <v>187.7217931756637</v>
+        <v>86.94754087686852</v>
       </c>
       <c r="I8" t="n">
-        <v>46.58366294279151</v>
+        <v>144.9834320545087</v>
       </c>
       <c r="J8" t="n">
-        <v>69.70315100612225</v>
+        <v>483.5210851839887</v>
       </c>
       <c r="K8" t="n">
-        <v>18.86526009605538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -735,34 +735,34 @@
         <v>80</v>
       </c>
       <c r="B9" t="n">
-        <v>0.04210161923399591</v>
+        <v>0.2044765721674873</v>
       </c>
       <c r="C9" t="n">
-        <v>14921.02160953662</v>
+        <v>167675.5725484803</v>
       </c>
       <c r="D9" t="n">
-        <v>11749.28398782329</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>8000</v>
       </c>
       <c r="F9" t="n">
-        <v>5877.521460140698</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>28792.78413721559</v>
+        <v>23707.64291318133</v>
       </c>
       <c r="H9" t="n">
-        <v>209.6553739323319</v>
+        <v>86.94754087687033</v>
       </c>
       <c r="I9" t="n">
-        <v>79.54494492920199</v>
+        <v>142.9882365903602</v>
       </c>
       <c r="J9" t="n">
-        <v>57.85730229289747</v>
+        <v>484.0705136350001</v>
       </c>
       <c r="K9" t="n">
-        <v>18.86526009605538</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/plot/sensitivity_D.xlsx
+++ b/plot/sensitivity_D.xlsx
@@ -490,34 +490,34 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1959842690694846</v>
+        <v>0.2440152182469439</v>
       </c>
       <c r="C2" t="n">
-        <v>167379.430045784</v>
+        <v>74992.69372329353</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>6567.526127315652</v>
       </c>
       <c r="E2" t="n">
         <v>1000</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1221.429532664919</v>
       </c>
       <c r="G2" t="n">
-        <v>16679.90064510335</v>
+        <v>13371.32058046708</v>
       </c>
       <c r="H2" t="n">
-        <v>86.00713363009163</v>
+        <v>33.79667052520301</v>
       </c>
       <c r="I2" t="n">
-        <v>143.0186325379542</v>
+        <v>75.85987059134024</v>
       </c>
       <c r="J2" t="n">
-        <v>485.7970673756182</v>
+        <v>211.2864944093303</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>21.97967244750888</v>
       </c>
     </row>
     <row r="3">
@@ -525,34 +525,34 @@
         <v>20</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1980936699523897</v>
+        <v>0.2992096776928113</v>
       </c>
       <c r="C3" t="n">
-        <v>168191.7169200724</v>
+        <v>38906.98065033667</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>9534.960877288318</v>
       </c>
       <c r="E3" t="n">
         <v>2000</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>888.6280889188932</v>
       </c>
       <c r="G3" t="n">
-        <v>17755.99468772663</v>
+        <v>14291.0912322915</v>
       </c>
       <c r="H3" t="n">
-        <v>86.94754087686988</v>
+        <v>4.395943813991729</v>
       </c>
       <c r="I3" t="n">
-        <v>144.9834320545083</v>
+        <v>67.26254334975933</v>
       </c>
       <c r="J3" t="n">
-        <v>483.5210851839864</v>
+        <v>104.7181413419963</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>31.91084630953253</v>
       </c>
     </row>
     <row r="4">
@@ -560,34 +560,34 @@
         <v>30</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1962923031382185</v>
+        <v>0.2954145188501849</v>
       </c>
       <c r="C4" t="n">
-        <v>165644.076801232</v>
+        <v>44935.92066178762</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>9013.347505076968</v>
       </c>
       <c r="E4" t="n">
         <v>3000</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>778.5963937281897</v>
       </c>
       <c r="G4" t="n">
-        <v>18517.33487192985</v>
+        <v>15444.29329452116</v>
       </c>
       <c r="H4" t="n">
-        <v>76.98933608601322</v>
+        <v>10.7681934879116</v>
       </c>
       <c r="I4" t="n">
-        <v>147.5793668631472</v>
+        <v>67.09614943668781</v>
       </c>
       <c r="J4" t="n">
-        <v>501.1777672711995</v>
+        <v>119.8945194034745</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>30.16515229276094</v>
       </c>
     </row>
     <row r="5">
@@ -595,34 +595,34 @@
         <v>40</v>
       </c>
       <c r="B5" t="n">
-        <v>0.2004215584482251</v>
+        <v>0.3127223436359816</v>
       </c>
       <c r="C5" t="n">
-        <v>168191.716920072</v>
+        <v>35673.24698190192</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>9509.62380368987</v>
       </c>
       <c r="E5" t="n">
         <v>4000</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>349.5666448706323</v>
       </c>
       <c r="G5" t="n">
-        <v>19755.9946877266</v>
+        <v>16501.88338090311</v>
       </c>
       <c r="H5" t="n">
-        <v>86.94754087686852</v>
+        <v>4.599026397902787</v>
       </c>
       <c r="I5" t="n">
-        <v>144.9834320545087</v>
+        <v>52.50678729800855</v>
       </c>
       <c r="J5" t="n">
-        <v>483.5210851839887</v>
+        <v>111.8658823413324</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>31.82605021315217</v>
       </c>
     </row>
     <row r="6">
@@ -630,34 +630,34 @@
         <v>50</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2011212020879525</v>
+        <v>0.2482182265340659</v>
       </c>
       <c r="C6" t="n">
-        <v>167792.8141298215</v>
+        <v>76260.24694757526</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>6820.391239989129</v>
       </c>
       <c r="E6" t="n">
         <v>5000</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1540.556581589423</v>
       </c>
       <c r="G6" t="n">
-        <v>20718.6259613755</v>
+        <v>17423.80148265012</v>
       </c>
       <c r="H6" t="n">
-        <v>74.78175886784675</v>
+        <v>42.13356860772264</v>
       </c>
       <c r="I6" t="n">
-        <v>158.6441210180155</v>
+        <v>81.41863723056635</v>
       </c>
       <c r="J6" t="n">
-        <v>502.2034833580587</v>
+        <v>175.2040221266206</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>22.82594123155665</v>
       </c>
     </row>
     <row r="7">
@@ -665,34 +665,34 @@
         <v>60</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2022851463358705</v>
+        <v>0.3157848429119558</v>
       </c>
       <c r="C7" t="n">
-        <v>167792.8141298217</v>
+        <v>34494.42664923065</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>9503.14795154877</v>
       </c>
       <c r="E7" t="n">
         <v>6000</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>270.6924135305871</v>
       </c>
       <c r="G7" t="n">
-        <v>21718.62596137552</v>
+        <v>18463.85131061578</v>
       </c>
       <c r="H7" t="n">
-        <v>74.78175886784811</v>
+        <v>4.672855992181219</v>
       </c>
       <c r="I7" t="n">
-        <v>158.6441210180144</v>
+        <v>50.33963124012855</v>
       </c>
       <c r="J7" t="n">
-        <v>502.2034833580567</v>
+        <v>108.0478076913914</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>31.80437734788745</v>
       </c>
     </row>
     <row r="8">
@@ -700,34 +700,34 @@
         <v>70</v>
       </c>
       <c r="B8" t="n">
-        <v>0.2039133911919788</v>
+        <v>0.2635974327393903</v>
       </c>
       <c r="C8" t="n">
-        <v>168191.716920072</v>
+        <v>71365.77301209127</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>7292.430859531986</v>
       </c>
       <c r="E8" t="n">
         <v>7000</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1368.296870582154</v>
       </c>
       <c r="G8" t="n">
-        <v>22755.9946877266</v>
+        <v>19609.59247082243</v>
       </c>
       <c r="H8" t="n">
-        <v>86.94754087686852</v>
+        <v>29.08728530111135</v>
       </c>
       <c r="I8" t="n">
-        <v>144.9834320545087</v>
+        <v>90.63680530130712</v>
       </c>
       <c r="J8" t="n">
-        <v>483.5210851839887</v>
+        <v>176.1966102120945</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>24.40572576817934</v>
       </c>
     </row>
     <row r="9">
@@ -735,34 +735,34 @@
         <v>80</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2044765721674873</v>
+        <v>0.3092050625014788</v>
       </c>
       <c r="C9" t="n">
-        <v>167675.5725484803</v>
+        <v>45188.64465077595</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>9353.217988147495</v>
       </c>
       <c r="E9" t="n">
         <v>8000</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>854.6512931178744</v>
       </c>
       <c r="G9" t="n">
-        <v>23707.64291318133</v>
+        <v>20731.78375292757</v>
       </c>
       <c r="H9" t="n">
-        <v>86.94754087687033</v>
+        <v>7.951311062127661</v>
       </c>
       <c r="I9" t="n">
-        <v>142.9882365903602</v>
+        <v>80.00942815720354</v>
       </c>
       <c r="J9" t="n">
-        <v>484.0705136350001</v>
+        <v>106.9293221455625</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>31.30260370865962</v>
       </c>
     </row>
   </sheetData>

--- a/plot/sensitivity_D.xlsx
+++ b/plot/sensitivity_D.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,52 +436,77 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Min Self-consumption Ratio</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Min RE Generation Ratio</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>LCOE (元/kWh)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Equipment Investment (万元, one-time)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Annual Grid Cost (万元/yr)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Connection Cost (万元, one-time)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Annual Market Revenue (万元/yr)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Annualized Objective (万元/yr)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>MIP Gap Target</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>MIP Gap Achieved</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Wind (MW)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>PV (MW)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Storage (MWh)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Grid (MW)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Output Directory</t>
         </is>
       </c>
     </row>
@@ -490,34 +515,51 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2440152182469439</v>
+        <v>0.6</v>
       </c>
       <c r="C2" t="n">
-        <v>74992.69372329353</v>
+        <v>0.3</v>
       </c>
       <c r="D2" t="n">
-        <v>6567.526127315652</v>
+        <v>0.2525481501980741</v>
       </c>
       <c r="E2" t="n">
+        <v>59028.87291760925</v>
+      </c>
+      <c r="F2" t="n">
+        <v>7993.725302380242</v>
+      </c>
+      <c r="G2" t="n">
         <v>1000</v>
       </c>
-      <c r="F2" t="n">
-        <v>1221.429532664919</v>
-      </c>
-      <c r="G2" t="n">
-        <v>13371.32058046708</v>
-      </c>
       <c r="H2" t="n">
-        <v>33.79667052520301</v>
+        <v>1715.833927998411</v>
       </c>
       <c r="I2" t="n">
-        <v>75.85987059134024</v>
+        <v>12807.64411811729</v>
       </c>
       <c r="J2" t="n">
-        <v>211.2864944093303</v>
+        <v>0.01</v>
       </c>
       <c r="K2" t="n">
-        <v>21.97967244750888</v>
+        <v>0.006875754358494111</v>
+      </c>
+      <c r="L2" t="n">
+        <v>23.63728833599275</v>
+      </c>
+      <c r="M2" t="n">
+        <v>74.11378245722905</v>
+      </c>
+      <c r="N2" t="n">
+        <v>148.6088802278065</v>
+      </c>
+      <c r="O2" t="n">
+        <v>26.75276205615878</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>results/sensitivity/D/D_10</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -525,34 +567,51 @@
         <v>20</v>
       </c>
       <c r="B3" t="n">
-        <v>0.2992096776928113</v>
+        <v>0.6</v>
       </c>
       <c r="C3" t="n">
-        <v>38906.98065033667</v>
+        <v>0.3</v>
       </c>
       <c r="D3" t="n">
-        <v>9534.960877288318</v>
+        <v>0.2826139870869598</v>
       </c>
       <c r="E3" t="n">
+        <v>41374.20918792896</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9325.385038302426</v>
+      </c>
+      <c r="G3" t="n">
         <v>2000</v>
       </c>
-      <c r="F3" t="n">
-        <v>888.6280889188932</v>
-      </c>
-      <c r="G3" t="n">
-        <v>14291.0912322915</v>
-      </c>
       <c r="H3" t="n">
-        <v>4.395943813991729</v>
+        <v>1348.067354575852</v>
       </c>
       <c r="I3" t="n">
-        <v>67.26254334975933</v>
+        <v>13853.20308469248</v>
       </c>
       <c r="J3" t="n">
-        <v>104.7181413419963</v>
+        <v>0.01</v>
       </c>
       <c r="K3" t="n">
-        <v>31.91084630953253</v>
+        <v>0.009648407609488669</v>
+      </c>
+      <c r="L3" t="n">
+        <v>9.134510758594843</v>
+      </c>
+      <c r="M3" t="n">
+        <v>65.49857942551672</v>
+      </c>
+      <c r="N3" t="n">
+        <v>105.7961029984235</v>
+      </c>
+      <c r="O3" t="n">
+        <v>31.20945461279259</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>results/sensitivity/D/D_20</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -560,34 +619,51 @@
         <v>30</v>
       </c>
       <c r="B4" t="n">
-        <v>0.2954145188501849</v>
+        <v>0.6</v>
       </c>
       <c r="C4" t="n">
-        <v>44935.92066178762</v>
+        <v>0.3</v>
       </c>
       <c r="D4" t="n">
-        <v>9013.347505076968</v>
+        <v>0.2794332573349456</v>
       </c>
       <c r="E4" t="n">
+        <v>44262.85607009488</v>
+      </c>
+      <c r="F4" t="n">
+        <v>9082.995419864528</v>
+      </c>
+      <c r="G4" t="n">
         <v>3000</v>
       </c>
-      <c r="F4" t="n">
-        <v>778.5963937281897</v>
-      </c>
-      <c r="G4" t="n">
-        <v>15444.29329452116</v>
-      </c>
       <c r="H4" t="n">
-        <v>10.7681934879116</v>
+        <v>1370.532274883478</v>
       </c>
       <c r="I4" t="n">
-        <v>67.09614943668781</v>
+        <v>14858.95345898053</v>
       </c>
       <c r="J4" t="n">
-        <v>119.8945194034745</v>
+        <v>0.01</v>
       </c>
       <c r="K4" t="n">
-        <v>30.16515229276094</v>
+        <v>0.009381921926922353</v>
+      </c>
+      <c r="L4" t="n">
+        <v>11.78053941813737</v>
+      </c>
+      <c r="M4" t="n">
+        <v>65.97855820246271</v>
+      </c>
+      <c r="N4" t="n">
+        <v>113.5745735063265</v>
+      </c>
+      <c r="O4" t="n">
+        <v>30.39824437705665</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>results/sensitivity/D/D_30</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -595,34 +671,51 @@
         <v>40</v>
       </c>
       <c r="B5" t="n">
-        <v>0.3127223436359816</v>
+        <v>0.6</v>
       </c>
       <c r="C5" t="n">
-        <v>35673.24698190192</v>
+        <v>0.3</v>
       </c>
       <c r="D5" t="n">
-        <v>9509.62380368987</v>
+        <v>0.2671848071036229</v>
       </c>
       <c r="E5" t="n">
+        <v>53133.72142790793</v>
+      </c>
+      <c r="F5" t="n">
+        <v>8607.42420682016</v>
+      </c>
+      <c r="G5" t="n">
         <v>4000</v>
       </c>
-      <c r="F5" t="n">
-        <v>349.5666448706323</v>
-      </c>
-      <c r="G5" t="n">
-        <v>16501.88338090311</v>
-      </c>
       <c r="H5" t="n">
-        <v>4.599026397902787</v>
+        <v>1710.724780040696</v>
       </c>
       <c r="I5" t="n">
-        <v>52.50678729800855</v>
+        <v>15874.20157663331</v>
       </c>
       <c r="J5" t="n">
-        <v>111.8658823413324</v>
+        <v>0.01</v>
       </c>
       <c r="K5" t="n">
-        <v>31.82605021315217</v>
+        <v>0.009736974148297691</v>
+      </c>
+      <c r="L5" t="n">
+        <v>26.26769692129827</v>
+      </c>
+      <c r="M5" t="n">
+        <v>69.71712116384658</v>
+      </c>
+      <c r="N5" t="n">
+        <v>107.415248259694</v>
+      </c>
+      <c r="O5" t="n">
+        <v>28.80664058507417</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>results/sensitivity/D/D_40</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -630,34 +723,51 @@
         <v>50</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2482182265340659</v>
+        <v>0.6</v>
       </c>
       <c r="C6" t="n">
-        <v>76260.24694757526</v>
+        <v>0.3</v>
       </c>
       <c r="D6" t="n">
-        <v>6820.391239989129</v>
+        <v>0.2430882847053844</v>
       </c>
       <c r="E6" t="n">
+        <v>69413.43308752358</v>
+      </c>
+      <c r="F6" t="n">
+        <v>7409.252504752736</v>
+      </c>
+      <c r="G6" t="n">
         <v>5000</v>
       </c>
-      <c r="F6" t="n">
-        <v>1540.556581589423</v>
-      </c>
-      <c r="G6" t="n">
-        <v>17423.80148265012</v>
-      </c>
       <c r="H6" t="n">
-        <v>42.13356860772264</v>
+        <v>2031.840396733106</v>
       </c>
       <c r="I6" t="n">
-        <v>81.41863723056635</v>
+        <v>16879.97776946437</v>
       </c>
       <c r="J6" t="n">
-        <v>175.2040221266206</v>
+        <v>0.01</v>
       </c>
       <c r="K6" t="n">
-        <v>22.82594123155665</v>
+        <v>0.009503602762166835</v>
+      </c>
+      <c r="L6" t="n">
+        <v>40.3269320116765</v>
+      </c>
+      <c r="M6" t="n">
+        <v>77.05182595728435</v>
+      </c>
+      <c r="N6" t="n">
+        <v>145.3611050118403</v>
+      </c>
+      <c r="O6" t="n">
+        <v>24.79669512969457</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>results/sensitivity/D/D_50</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -665,34 +775,51 @@
         <v>60</v>
       </c>
       <c r="B7" t="n">
-        <v>0.3157848429119558</v>
+        <v>0.6</v>
       </c>
       <c r="C7" t="n">
-        <v>34494.42664923065</v>
+        <v>0.3</v>
       </c>
       <c r="D7" t="n">
-        <v>9503.14795154877</v>
+        <v>0.3024886011136251</v>
       </c>
       <c r="E7" t="n">
+        <v>31816.24672889062</v>
+      </c>
+      <c r="F7" t="n">
+        <v>9778.0770211706</v>
+      </c>
+      <c r="G7" t="n">
         <v>6000</v>
       </c>
-      <c r="F7" t="n">
-        <v>270.6924135305871</v>
-      </c>
-      <c r="G7" t="n">
-        <v>18463.85131061578</v>
-      </c>
       <c r="H7" t="n">
-        <v>4.672855992181219</v>
+        <v>895.4316979756844</v>
       </c>
       <c r="I7" t="n">
-        <v>50.33963124012855</v>
+        <v>17863.15247077357</v>
       </c>
       <c r="J7" t="n">
-        <v>108.0478076913914</v>
+        <v>0.01</v>
       </c>
       <c r="K7" t="n">
-        <v>31.80437734788745</v>
+        <v>0.008038592646916755</v>
+      </c>
+      <c r="L7" t="n">
+        <v>4.671862066754549</v>
+      </c>
+      <c r="M7" t="n">
+        <v>49.80339060137182</v>
+      </c>
+      <c r="N7" t="n">
+        <v>91.19612301436288</v>
+      </c>
+      <c r="O7" t="n">
+        <v>32.72448802265931</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>results/sensitivity/D/D_60</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -700,34 +827,51 @@
         <v>70</v>
       </c>
       <c r="B8" t="n">
-        <v>0.2635974327393903</v>
+        <v>0.6</v>
       </c>
       <c r="C8" t="n">
-        <v>71365.77301209127</v>
+        <v>0.3</v>
       </c>
       <c r="D8" t="n">
-        <v>7292.430859531986</v>
+        <v>0.2439943738310816</v>
       </c>
       <c r="E8" t="n">
+        <v>70416.13438715608</v>
+      </c>
+      <c r="F8" t="n">
+        <v>7338.808411484083</v>
+      </c>
+      <c r="G8" t="n">
         <v>7000</v>
       </c>
-      <c r="F8" t="n">
-        <v>1368.296870582154</v>
-      </c>
-      <c r="G8" t="n">
-        <v>19609.59247082243</v>
-      </c>
       <c r="H8" t="n">
-        <v>29.08728530111135</v>
+        <v>2050.365780648838</v>
       </c>
       <c r="I8" t="n">
-        <v>90.63680530130712</v>
+        <v>18884.94012578331</v>
       </c>
       <c r="J8" t="n">
-        <v>176.1966102120945</v>
+        <v>0.01</v>
       </c>
       <c r="K8" t="n">
-        <v>24.40572576817934</v>
+        <v>0.008757680218061004</v>
+      </c>
+      <c r="L8" t="n">
+        <v>28.82537292157001</v>
+      </c>
+      <c r="M8" t="n">
+        <v>89.01466169734179</v>
+      </c>
+      <c r="N8" t="n">
+        <v>174.1452057567077</v>
+      </c>
+      <c r="O8" t="n">
+        <v>24.56093845878208</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>results/sensitivity/D/D_70</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -735,34 +879,51 @@
         <v>80</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3092050625014788</v>
+        <v>0.6</v>
       </c>
       <c r="C9" t="n">
-        <v>45188.64465077595</v>
+        <v>0.3</v>
       </c>
       <c r="D9" t="n">
-        <v>9353.217988147495</v>
+        <v>0.2759327564562994</v>
       </c>
       <c r="E9" t="n">
+        <v>51175.03963838699</v>
+      </c>
+      <c r="F9" t="n">
+        <v>8808.13585740196</v>
+      </c>
+      <c r="G9" t="n">
         <v>8000</v>
       </c>
-      <c r="F9" t="n">
-        <v>854.6512931178744</v>
-      </c>
-      <c r="G9" t="n">
-        <v>20731.78375292757</v>
-      </c>
       <c r="H9" t="n">
-        <v>7.951311062127661</v>
+        <v>1692.457943471835</v>
       </c>
       <c r="I9" t="n">
-        <v>80.00942815720354</v>
+        <v>19909.69314519034</v>
       </c>
       <c r="J9" t="n">
-        <v>106.9293221455625</v>
+        <v>0.01</v>
       </c>
       <c r="K9" t="n">
-        <v>31.30260370865962</v>
+        <v>0.009551506954153466</v>
+      </c>
+      <c r="L9" t="n">
+        <v>19.85990492844621</v>
+      </c>
+      <c r="M9" t="n">
+        <v>74.33887907524587</v>
+      </c>
+      <c r="N9" t="n">
+        <v>110.6912837524393</v>
+      </c>
+      <c r="O9" t="n">
+        <v>29.47836632329973</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>results/sensitivity/D/D_80</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/plot/sensitivity_D.xlsx
+++ b/plot/sensitivity_D.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,40 +521,40 @@
         <v>0.3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2525481501980741</v>
+        <v>0.4365979606087417</v>
       </c>
       <c r="E2" t="n">
-        <v>59028.87291760925</v>
+        <v>602.1248567035294</v>
       </c>
       <c r="F2" t="n">
-        <v>7993.725302380242</v>
+        <v>14940</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1715.833927998411</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>12807.64411811729</v>
+        <v>15996.40632141283</v>
       </c>
       <c r="J2" t="n">
         <v>0.01</v>
       </c>
       <c r="K2" t="n">
-        <v>0.006875754358494111</v>
+        <v>8.439395529701378e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>23.63728833599275</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>74.11378245722905</v>
+        <v>0.007082855678431419</v>
       </c>
       <c r="N2" t="n">
-        <v>148.6088802278065</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>26.75276205615878</v>
+        <v>50</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -573,40 +573,40 @@
         <v>0.3</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2826139870869598</v>
+        <v>0.4377619048566597</v>
       </c>
       <c r="E3" t="n">
-        <v>41374.20918792896</v>
+        <v>602.1248567035294</v>
       </c>
       <c r="F3" t="n">
-        <v>9325.385038302426</v>
+        <v>14940</v>
       </c>
       <c r="G3" t="n">
         <v>2000</v>
       </c>
       <c r="H3" t="n">
-        <v>1348.067354575852</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>13853.20308469248</v>
+        <v>16996.40632141283</v>
       </c>
       <c r="J3" t="n">
         <v>0.01</v>
       </c>
       <c r="K3" t="n">
-        <v>0.009648407609488669</v>
+        <v>7.942855533426517e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>9.134510758594843</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>65.49857942551672</v>
+        <v>0.007082855678431419</v>
       </c>
       <c r="N3" t="n">
-        <v>105.7961029984235</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>31.20945461279259</v>
+        <v>50</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -625,40 +625,40 @@
         <v>0.3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2794332573349456</v>
+        <v>0.4389258491045775</v>
       </c>
       <c r="E4" t="n">
-        <v>44262.85607009488</v>
+        <v>602.1248567035294</v>
       </c>
       <c r="F4" t="n">
-        <v>9082.995419864528</v>
+        <v>14940</v>
       </c>
       <c r="G4" t="n">
         <v>3000</v>
       </c>
       <c r="H4" t="n">
-        <v>1370.532274883478</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>14858.95345898053</v>
+        <v>17996.40632141283</v>
       </c>
       <c r="J4" t="n">
         <v>0.01</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009381921926922353</v>
+        <v>7.501497664996096e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>11.78053941813737</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>65.97855820246271</v>
+        <v>0.007082855678431419</v>
       </c>
       <c r="N4" t="n">
-        <v>113.5745735063265</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>30.39824437705665</v>
+        <v>50</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -677,40 +677,40 @@
         <v>0.3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2671848071036229</v>
+        <v>0.4400897933524955</v>
       </c>
       <c r="E5" t="n">
-        <v>53133.72142790793</v>
+        <v>602.1248567035294</v>
       </c>
       <c r="F5" t="n">
-        <v>8607.42420682016</v>
+        <v>14940</v>
       </c>
       <c r="G5" t="n">
         <v>4000</v>
       </c>
       <c r="H5" t="n">
-        <v>1710.724780040696</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>15874.20157663331</v>
+        <v>18996.40632141283</v>
       </c>
       <c r="J5" t="n">
         <v>0.01</v>
       </c>
       <c r="K5" t="n">
-        <v>0.009736974148297691</v>
+        <v>7.10660730846901e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>26.26769692129827</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>69.71712116384658</v>
+        <v>0.007082855678431419</v>
       </c>
       <c r="N5" t="n">
-        <v>107.415248259694</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>28.80664058507417</v>
+        <v>50</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -729,40 +729,40 @@
         <v>0.3</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2430882847053844</v>
+        <v>0.4412537376004133</v>
       </c>
       <c r="E6" t="n">
-        <v>69413.43308752358</v>
+        <v>602.1248567035294</v>
       </c>
       <c r="F6" t="n">
-        <v>7409.252504752736</v>
+        <v>14940</v>
       </c>
       <c r="G6" t="n">
         <v>5000</v>
       </c>
       <c r="H6" t="n">
-        <v>2031.840396733106</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>16879.97776946437</v>
+        <v>19996.40632141283</v>
       </c>
       <c r="J6" t="n">
         <v>0.01</v>
       </c>
       <c r="K6" t="n">
-        <v>0.009503602762166835</v>
+        <v>6.75121308441491e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>40.3269320116765</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>77.05182595728435</v>
+        <v>0.007082855678431419</v>
       </c>
       <c r="N6" t="n">
-        <v>145.3611050118403</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>24.79669512969457</v>
+        <v>50</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -781,40 +781,40 @@
         <v>0.3</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3024886011136251</v>
+        <v>0.4424176818483312</v>
       </c>
       <c r="E7" t="n">
-        <v>31816.24672889062</v>
+        <v>602.1248567035294</v>
       </c>
       <c r="F7" t="n">
-        <v>9778.0770211706</v>
+        <v>14940</v>
       </c>
       <c r="G7" t="n">
         <v>6000</v>
       </c>
       <c r="H7" t="n">
-        <v>895.4316979756844</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>17863.15247077357</v>
+        <v>20996.40632141283</v>
       </c>
       <c r="J7" t="n">
         <v>0.01</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008038592646916755</v>
+        <v>6.429671722475757e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>4.671862066754549</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>49.80339060137182</v>
+        <v>0.007082855678431419</v>
       </c>
       <c r="N7" t="n">
-        <v>91.19612301436288</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>32.72448802265931</v>
+        <v>50</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -833,40 +833,40 @@
         <v>0.3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2439943738310816</v>
+        <v>0.4435816260962491</v>
       </c>
       <c r="E8" t="n">
-        <v>70416.13438715608</v>
+        <v>602.1248567035294</v>
       </c>
       <c r="F8" t="n">
-        <v>7338.808411484083</v>
+        <v>14940</v>
       </c>
       <c r="G8" t="n">
         <v>7000</v>
       </c>
       <c r="H8" t="n">
-        <v>2050.365780648838</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>18884.94012578331</v>
+        <v>21996.40632141283</v>
       </c>
       <c r="J8" t="n">
         <v>0.01</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008757680218061004</v>
+        <v>6.137366169081035e-06</v>
       </c>
       <c r="L8" t="n">
-        <v>28.82537292157001</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>89.01466169734179</v>
+        <v>0.007082855678431419</v>
       </c>
       <c r="N8" t="n">
-        <v>174.1452057567077</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>24.56093845878208</v>
+        <v>50</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -885,44 +885,96 @@
         <v>0.3</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2759327564562994</v>
+        <v>0.4447455703441671</v>
       </c>
       <c r="E9" t="n">
-        <v>51175.03963838699</v>
+        <v>602.1248567035294</v>
       </c>
       <c r="F9" t="n">
-        <v>8808.13585740196</v>
+        <v>14940</v>
       </c>
       <c r="G9" t="n">
         <v>8000</v>
       </c>
       <c r="H9" t="n">
-        <v>1692.457943471835</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>19909.69314519034</v>
+        <v>22996.40632141283</v>
       </c>
       <c r="J9" t="n">
         <v>0.01</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009551506954153466</v>
+        <v>5.8704824619791e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>19.85990492844621</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>74.33887907524587</v>
+        <v>0.007082855678431419</v>
       </c>
       <c r="N9" t="n">
-        <v>110.6912837524393</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>29.47836632329973</v>
+        <v>50</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>results/sensitivity/D/D_80</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>90</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.4459095145920849</v>
+      </c>
+      <c r="E10" t="n">
+        <v>602.1248567035294</v>
+      </c>
+      <c r="F10" t="n">
+        <v>14940</v>
+      </c>
+      <c r="G10" t="n">
+        <v>9000</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>23996.40632141283</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.625842394489466e-06</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.007082855678431419</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>50</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>results/sensitivity/D/D_90</t>
         </is>
       </c>
     </row>
